--- a/Backend/media/planillas_excel/reportes_diarios.xlsx
+++ b/Backend/media/planillas_excel/reportes_diarios.xlsx
@@ -431,13 +431,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="3" max="3"/>
+    <col width="13" customWidth="1" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -465,44 +465,66 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>2026-02-17</t>
+          <t>2026-02-18</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1000.00</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>550026.76</t>
+          <t>449390.00</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>-550026.76</t>
+          <t>-448390.00</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2026-02-18</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>1000.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
         <is>
-          <t>191078.23</t>
+          <t>3637166.51</t>
         </is>
       </c>
       <c r="D3" s="3" t="inlineStr">
         <is>
-          <t>-190078.23</t>
+          <t>-3637166.51</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>2026-02-22</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>123.00</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>96108.98</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-95985.98</t>
         </is>
       </c>
     </row>
